--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F8E439-5229-4890-9BBB-D8A3E2B877E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208AFFD6-B64C-4C3C-AB0E-3C8ECE740257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="156" windowWidth="21156" windowHeight="12828" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="B 2023-2026" sheetId="10" r:id="rId1"/>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="12">
-        <v>46095</v>
+        <v>46109</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>7</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
-        <v>45730</v>
+        <v>45744</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>7</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
-        <v>46095</v>
+        <v>46109</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>7</v>

--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208AFFD6-B64C-4C3C-AB0E-3C8ECE740257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912C4321-3634-4597-B68F-14D9C3DDFD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="141">
   <si>
     <t>päivä</t>
   </si>
@@ -456,6 +456,12 @@
   </si>
   <si>
     <t>OsVa1</t>
+  </si>
+  <si>
+    <t>16-25,20-25</t>
+  </si>
+  <si>
+    <t>12-25,7-25</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1061,7 @@
       </c>
       <c r="C4" s="11">
         <f>'B 2025-2026'!R2</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" s="11">
         <f>'B 2025-2026'!O2</f>
@@ -1067,23 +1073,23 @@
       </c>
       <c r="F4" s="11">
         <f>'B 2025-2026'!Q2</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G4" s="11">
         <f>'B 2025-2026'!O3</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" s="11">
         <f>'B 2025-2026'!Q3</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I4" s="11">
         <f>'B 2025-2026'!O4</f>
-        <v>900</v>
+        <v>988</v>
       </c>
       <c r="J4" s="11">
         <f>'B 2025-2026'!Q4</f>
-        <v>837</v>
+        <v>987</v>
       </c>
       <c r="K4" s="11"/>
     </row>
@@ -1094,7 +1100,7 @@
       </c>
       <c r="C5" s="7">
         <f t="shared" ref="C5:J5" si="0">SUM(C2:C4)</f>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
@@ -1106,23 +1112,23 @@
       </c>
       <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G5" s="9">
         <f t="shared" si="0"/>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H5" s="9">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" si="0"/>
-        <v>3214</v>
+        <v>3302</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="0"/>
-        <v>3195</v>
+        <v>3345</v>
       </c>
       <c r="K5" s="8"/>
     </row>
@@ -1239,15 +1245,15 @@
       </c>
       <c r="Q2" s="16">
         <f>SUM(J2:J24)+I9</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R2" s="16">
         <f>SUM(O2:Q2)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S2" s="16">
         <f>R2*2</f>
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1287,16 +1293,16 @@
       </c>
       <c r="O3" s="13">
         <f>SUM(H2:H24)*2+SUM(I2:I24)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P3" s="13"/>
       <c r="Q3" s="13">
         <f>SUM(J2:J24)*2+SUM(I10:I13)+H8+I9*2</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="R3" s="13">
         <f>SUM(O3:Q3)</f>
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="S3" s="13"/>
     </row>
@@ -1337,16 +1343,16 @@
       </c>
       <c r="O4" s="16">
         <f>SUM(K2:K24)</f>
-        <v>900</v>
+        <v>988</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="16">
         <f>SUM(L2:L24)</f>
-        <v>837</v>
+        <v>987</v>
       </c>
       <c r="R4" s="16">
         <f>SUM(O4:Q4)</f>
-        <v>1737</v>
+        <v>1975</v>
       </c>
       <c r="S4" s="16"/>
     </row>
@@ -1839,10 +1845,10 @@
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="13">
-        <v>1</v>
-      </c>
-      <c r="J17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13">
+        <v>1</v>
+      </c>
       <c r="K17" s="13">
         <v>60</v>
       </c>
@@ -1877,7 +1883,9 @@
         <v>134</v>
       </c>
       <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
+      <c r="H18" s="16">
+        <v>1</v>
+      </c>
       <c r="I18" s="16"/>
       <c r="J18" s="16"/>
       <c r="K18" s="16">
@@ -1907,16 +1915,24 @@
       <c r="D19" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
+      <c r="E19" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>139</v>
+      </c>
       <c r="G19" s="13"/>
-      <c r="H19" s="13">
-        <v>1</v>
-      </c>
+      <c r="H19" s="13"/>
       <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
+      <c r="J19" s="13">
+        <v>1</v>
+      </c>
+      <c r="K19" s="13">
+        <v>36</v>
+      </c>
+      <c r="L19" s="13">
+        <v>50</v>
+      </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
@@ -1938,14 +1954,24 @@
       <c r="D20" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="16"/>
+      <c r="E20" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>140</v>
+      </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
+      <c r="J20" s="16">
+        <v>1</v>
+      </c>
+      <c r="K20" s="16">
+        <v>19</v>
+      </c>
+      <c r="L20" s="16">
+        <v>50</v>
+      </c>
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
@@ -1967,14 +1993,24 @@
       <c r="D21" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="13"/>
+      <c r="E21" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>104</v>
+      </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
+      <c r="J21" s="13">
+        <v>1</v>
+      </c>
+      <c r="K21" s="13">
+        <v>33</v>
+      </c>
+      <c r="L21" s="13">
+        <v>50</v>
+      </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>

--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912C4321-3634-4597-B68F-14D9C3DDFD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5577F066-6F3D-410E-8172-E69F1D8FA34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="142">
   <si>
     <t>päivä</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>12-25,7-25</t>
+  </si>
+  <si>
+    <t>Lempo</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1149,9 @@
   <dimension ref="A1:S24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="19" width="10.77734375" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="19" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -2020,10 +2025,18 @@
       <c r="S21" s="13"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
+      <c r="A22" s="15">
+        <v>46137</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>141</v>
+      </c>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
@@ -2040,11 +2053,19 @@
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
+    <row r="23" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>46137</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>127</v>
+      </c>
       <c r="E23" s="14"/>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
@@ -2062,10 +2083,18 @@
       <c r="S23" s="13"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
+      <c r="A24" s="15">
+        <v>46137</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>117</v>
+      </c>
       <c r="E24" s="17"/>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>

--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5577F066-6F3D-410E-8172-E69F1D8FA34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BE3252-4BFC-490C-848E-1EED623CF2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1548" yWindow="420" windowWidth="19212" windowHeight="12228" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="B 2023-2026" sheetId="10" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="145">
   <si>
     <t>päivä</t>
   </si>
@@ -465,6 +465,15 @@
   </si>
   <si>
     <t>Lempo</t>
+  </si>
+  <si>
+    <t>21-25,24-26</t>
+  </si>
+  <si>
+    <t>25-13,25-14</t>
+  </si>
+  <si>
+    <t>25-20,21-25,15-11</t>
   </si>
 </sst>
 </file>
@@ -1064,11 +1073,11 @@
       </c>
       <c r="C4" s="11">
         <f>'B 2025-2026'!R2</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" s="11">
         <f>'B 2025-2026'!O2</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" s="11">
         <f>'B 2025-2026'!P2</f>
@@ -1076,23 +1085,23 @@
       </c>
       <c r="F4" s="11">
         <f>'B 2025-2026'!Q2</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="11">
         <f>'B 2025-2026'!O3</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H4" s="11">
         <f>'B 2025-2026'!Q3</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="11">
         <f>'B 2025-2026'!O4</f>
-        <v>988</v>
+        <v>1146</v>
       </c>
       <c r="J4" s="11">
         <f>'B 2025-2026'!Q4</f>
-        <v>987</v>
+        <v>1122</v>
       </c>
       <c r="K4" s="11"/>
     </row>
@@ -1103,11 +1112,11 @@
       </c>
       <c r="C5" s="7">
         <f t="shared" ref="C5:J5" si="0">SUM(C2:C4)</f>
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="7">
         <f t="shared" si="0"/>
@@ -1115,23 +1124,23 @@
       </c>
       <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="9">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H5" s="9">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" si="0"/>
-        <v>3302</v>
+        <v>3460</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="0"/>
-        <v>3345</v>
+        <v>3480</v>
       </c>
       <c r="K5" s="8"/>
     </row>
@@ -1242,7 +1251,7 @@
       </c>
       <c r="O2" s="16">
         <f>SUM(H2:H24)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P2" s="16">
         <f>SUM(I10:I13)</f>
@@ -1250,15 +1259,15 @@
       </c>
       <c r="Q2" s="16">
         <f>SUM(J2:J24)+I9</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R2" s="16">
         <f>SUM(O2:Q2)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S2" s="16">
         <f>R2*2</f>
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1298,16 +1307,16 @@
       </c>
       <c r="O3" s="13">
         <f>SUM(H2:H24)*2+SUM(I2:I24)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P3" s="13"/>
       <c r="Q3" s="13">
         <f>SUM(J2:J24)*2+SUM(I10:I13)+H8+I9*2</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R3" s="13">
         <f>SUM(O3:Q3)</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="S3" s="13"/>
     </row>
@@ -1348,16 +1357,16 @@
       </c>
       <c r="O4" s="16">
         <f>SUM(K2:K24)</f>
-        <v>988</v>
+        <v>1146</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="16">
         <f>SUM(L2:L24)</f>
-        <v>987</v>
+        <v>1122</v>
       </c>
       <c r="R4" s="16">
         <f>SUM(O4:Q4)</f>
-        <v>1975</v>
+        <v>2268</v>
       </c>
       <c r="S4" s="16"/>
     </row>
@@ -2037,14 +2046,24 @@
       <c r="D22" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="16"/>
+      <c r="E22" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>142</v>
+      </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
+      <c r="J22" s="16">
+        <v>1</v>
+      </c>
+      <c r="K22" s="16">
+        <v>47</v>
+      </c>
+      <c r="L22" s="16">
+        <v>51</v>
+      </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
@@ -2053,7 +2072,7 @@
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
     </row>
-    <row r="23" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
         <v>46137</v>
       </c>
@@ -2066,14 +2085,24 @@
       <c r="D23" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="13"/>
+      <c r="E23" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>143</v>
+      </c>
       <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="H23" s="13">
+        <v>1</v>
+      </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
+      <c r="K23" s="13">
+        <v>50</v>
+      </c>
+      <c r="L23" s="13">
+        <v>27</v>
+      </c>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
@@ -2082,7 +2111,7 @@
       <c r="R23" s="13"/>
       <c r="S23" s="13"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>46137</v>
       </c>
@@ -2095,14 +2124,24 @@
       <c r="D24" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="16"/>
+      <c r="E24" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>144</v>
+      </c>
       <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
+      <c r="H24" s="16">
+        <v>1</v>
+      </c>
       <c r="I24" s="16"/>
       <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
+      <c r="K24" s="16">
+        <v>61</v>
+      </c>
+      <c r="L24" s="16">
+        <v>57</v>
+      </c>
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
       <c r="O24" s="16"/>

--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BE3252-4BFC-490C-848E-1EED623CF2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF2626A-4AE9-462E-A881-92401A1D93B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1548" yWindow="420" windowWidth="19212" windowHeight="12228" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1200" yWindow="72" windowWidth="21096" windowHeight="12228" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="B 2023-2026" sheetId="10" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>sijoitus</t>
   </si>
   <si>
-    <t>pisteet I-V</t>
-  </si>
-  <si>
     <t>eräpisteet I-V</t>
   </si>
   <si>
@@ -474,6 +471,9 @@
   </si>
   <si>
     <t>25-20,21-25,15-11</t>
+  </si>
+  <si>
+    <t>pisteet I-V/A-V</t>
   </si>
 </sst>
 </file>
@@ -963,13 +963,13 @@
         <v>26</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>27</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>28</v>
@@ -980,10 +980,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="11">
         <f>'B 2023-2024'!Q2</f>
@@ -1026,7 +1026,7 @@
         <v>20</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="8">
         <f>'B 2024-2025'!Q2</f>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="C4" s="11">
         <f>'B 2025-2026'!R2</f>
@@ -1199,7 +1199,7 @@
       <c r="M1" s="18"/>
       <c r="N1" s="18"/>
       <c r="O1" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P1" s="18" t="s">
         <v>19</v>
@@ -1222,16 +1222,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16">
@@ -1278,16 +1278,16 @@
         <v>7</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13">
@@ -1328,16 +1328,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -1378,16 +1378,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13">
@@ -1417,16 +1417,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -1456,16 +1456,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -1495,16 +1495,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16">
@@ -1534,16 +1534,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -1573,16 +1573,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
@@ -1612,16 +1612,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
@@ -1651,16 +1651,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
@@ -1690,16 +1690,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
@@ -1729,16 +1729,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16">
@@ -1768,16 +1768,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13">
@@ -1807,16 +1807,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16">
@@ -1846,16 +1846,16 @@
         <v>7</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
@@ -1885,16 +1885,16 @@
         <v>7</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G18" s="16"/>
       <c r="H18" s="16">
@@ -1924,16 +1924,16 @@
         <v>7</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
@@ -1963,16 +1963,16 @@
         <v>7</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
@@ -2002,16 +2002,16 @@
         <v>7</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
@@ -2041,16 +2041,16 @@
         <v>7</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
@@ -2080,16 +2080,16 @@
         <v>7</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="13">
@@ -2119,16 +2119,16 @@
         <v>7</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="16">
@@ -2200,7 +2200,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="N1" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>19</v>
@@ -2223,13 +2223,13 @@
         <v>20</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
@@ -2274,13 +2274,13 @@
         <v>20</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -2322,13 +2322,13 @@
         <v>20</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -2370,13 +2370,13 @@
         <v>20</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
@@ -2407,13 +2407,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -2444,13 +2444,13 @@
         <v>20</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="13">
         <v>1</v>
@@ -2481,13 +2481,13 @@
         <v>20</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -2518,13 +2518,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="13">
         <v>1</v>
@@ -2555,13 +2555,13 @@
         <v>20</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
@@ -2592,13 +2592,13 @@
         <v>20</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="13">
         <v>1</v>
@@ -2629,13 +2629,13 @@
         <v>20</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" s="16">
         <v>1</v>
@@ -2666,13 +2666,13 @@
         <v>20</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G13" s="13">
         <v>1</v>
@@ -2703,13 +2703,13 @@
         <v>20</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G14" s="16">
         <v>1</v>
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
@@ -2777,13 +2777,13 @@
         <v>20</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
@@ -2820,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
@@ -2851,13 +2851,13 @@
         <v>20</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G18" s="16">
         <v>1</v>
@@ -2888,13 +2888,13 @@
         <v>20</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
@@ -2925,13 +2925,13 @@
         <v>20</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
@@ -2962,13 +2962,13 @@
         <v>20</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13">
         <v>1</v>
@@ -2999,13 +2999,13 @@
         <v>20</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
@@ -3036,13 +3036,13 @@
         <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
@@ -3073,13 +3073,13 @@
         <v>20</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
@@ -3189,7 +3189,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="N1" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>19</v>
@@ -3210,16 +3210,16 @@
         <v>15</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>39</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>40</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16">
@@ -3261,7 +3261,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>14</v>
@@ -3270,7 +3270,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="13">
         <v>1</v>
@@ -3309,16 +3309,16 @@
         <v>15</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16">
@@ -3357,16 +3357,16 @@
         <v>15</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="13">
         <v>1</v>
@@ -3394,7 +3394,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>17</v>
@@ -3403,7 +3403,7 @@
         <v>16</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="16">
         <v>1</v>
@@ -3431,16 +3431,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="13">
         <v>1</v>
@@ -3468,16 +3468,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8" s="16">
         <v>1</v>
@@ -3505,16 +3505,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13">
@@ -3542,16 +3542,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="16">
         <v>1</v>
@@ -3579,16 +3579,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11" s="13">
         <v>1</v>
@@ -3616,7 +3616,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>11</v>
@@ -3625,7 +3625,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12" s="16">
         <v>1</v>
@@ -3653,16 +3653,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" s="13">
         <v>1</v>
@@ -3690,16 +3690,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14" s="16">
         <v>1</v>
@@ -3727,16 +3727,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
@@ -3764,16 +3764,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
@@ -3801,7 +3801,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>18</v>
@@ -3810,7 +3810,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="13">
         <v>1</v>
@@ -3838,16 +3838,16 @@
         <v>7</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" s="16">
         <v>1</v>
@@ -3875,16 +3875,16 @@
         <v>7</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" s="13">
         <v>1</v>
@@ -3912,16 +3912,16 @@
         <v>7</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
@@ -3949,16 +3949,16 @@
         <v>7</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" s="13">
         <v>1</v>
@@ -3986,16 +3986,16 @@
         <v>7</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
@@ -4023,16 +4023,16 @@
         <v>7</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
@@ -4060,16 +4060,16 @@
         <v>7</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
@@ -4097,16 +4097,16 @@
         <v>7</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G25" s="13">
         <v>1</v>
@@ -4134,16 +4134,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
@@ -4171,7 +4171,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>18</v>
@@ -4180,7 +4180,7 @@
         <v>8</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>

--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF2626A-4AE9-462E-A881-92401A1D93B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC0BBA9-C86F-4891-8ABB-E174A534FEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="72" windowWidth="21096" windowHeight="12228" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1596" yWindow="540" windowWidth="21072" windowHeight="12948" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
-    <sheet name="B 2023-2026" sheetId="10" r:id="rId1"/>
-    <sheet name="B 2025-2026" sheetId="19" r:id="rId2"/>
-    <sheet name="B 2024-2025" sheetId="18" r:id="rId3"/>
-    <sheet name="B 2023-2024" sheetId="17" r:id="rId4"/>
+    <sheet name="B 2023-2027" sheetId="10" r:id="rId1"/>
+    <sheet name="B 2026-2027" sheetId="20" r:id="rId2"/>
+    <sheet name="B 2025-2026" sheetId="19" r:id="rId3"/>
+    <sheet name="B 2024-2025" sheetId="18" r:id="rId4"/>
+    <sheet name="B 2023-2024" sheetId="17" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="146">
   <si>
     <t>päivä</t>
   </si>
@@ -474,6 +475,9 @@
   </si>
   <si>
     <t>pisteet I-V/A-V</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
   </si>
 </sst>
 </file>
@@ -501,17 +505,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -567,7 +569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -581,10 +583,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -604,7 +604,7 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -613,13 +613,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,212 +940,255 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="9">
         <f>'B 2023-2024'!Q2</f>
         <v>26</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="9">
         <f>'B 2023-2024'!N2</f>
         <v>15</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="9">
         <f>'B 2023-2024'!O2</f>
         <v>3</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="9">
         <f>'B 2023-2024'!P2</f>
         <v>8</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="9">
         <f>'B 2023-2024'!N3</f>
         <v>33</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="9">
         <f>'B 2023-2024'!P3</f>
         <v>19</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <f>'B 2023-2024'!N4</f>
         <v>1264</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="9">
         <f>'B 2023-2024'!P4</f>
         <v>1211</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <f>'B 2024-2025'!Q2</f>
         <v>23</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <f>'B 2024-2025'!N2</f>
         <v>8</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <f>'B 2024-2025'!O3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <f>'B 2024-2025'!P2</f>
         <v>15</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <f>'B 2024-2025'!N3</f>
         <v>16</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <f>'B 2024-2025'!P3</f>
         <v>30</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="7">
         <f>'B 2024-2025'!N4</f>
         <v>1050</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="7">
         <f>'B 2024-2025'!P4</f>
         <v>1147</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="7">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <f>'B 2025-2026'!R2</f>
         <v>23</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9">
         <f>'B 2025-2026'!O2</f>
         <v>10</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <f>'B 2025-2026'!P2</f>
         <v>4</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <f>'B 2025-2026'!Q2</f>
         <v>9</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="9">
         <f>'B 2025-2026'!O3</f>
         <v>25</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="9">
         <f>'B 2025-2026'!Q3</f>
         <v>23</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="9">
         <f>'B 2025-2026'!O4</f>
         <v>1146</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="9">
         <f>'B 2025-2026'!Q4</f>
         <v>1122</v>
       </c>
-      <c r="K4" s="11"/>
+      <c r="K4" s="9">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="23">
+        <f>'B 2026-2027'!R3</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="23">
+        <f>'B 2026-2027'!O3</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="23">
+        <f>'B 2026-2027'!P3</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="23">
+        <f>'B 2026-2027'!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="23">
+        <f>'B 2026-2027'!O4</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <f>'B 2025-2026'!Q4</f>
+        <v>1122</v>
+      </c>
+      <c r="I5" s="23">
+        <f>'B 2025-2026'!O5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="23">
+        <f>'B 2025-2026'!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="22"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7">
-        <f t="shared" ref="C5:J5" si="0">SUM(C2:C4)</f>
+      <c r="C6" s="24">
+        <f>SUM(C2:C5)</f>
         <v>72</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D6" s="24">
+        <f t="shared" ref="D6:J6" si="0">SUM(D2:D5)</f>
+        <v>33</v>
+      </c>
+      <c r="E6" s="24">
         <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="F5" s="7">
+        <v>7</v>
+      </c>
+      <c r="F6" s="24">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G6" s="24">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H6" s="24">
         <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="I5" s="9">
+        <v>1194</v>
+      </c>
+      <c r="I6" s="24">
         <f t="shared" si="0"/>
         <v>3460</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J6" s="24">
         <f t="shared" si="0"/>
         <v>3480</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K6" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1151,6 +1197,604 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24860E15-68A6-4F46-9CFB-87CEA47F9577}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:S24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="19" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="16">
+        <v>3</v>
+      </c>
+      <c r="H1" s="16">
+        <v>2</v>
+      </c>
+      <c r="I1" s="16">
+        <v>1</v>
+      </c>
+      <c r="J1" s="16">
+        <v>0</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
+        <v>45934</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="14">
+        <f>SUM(H2:H24)</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="14">
+        <f>SUM(I10:I13)</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="14">
+        <f>SUM(J2:J24)+I9</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="14">
+        <f>SUM(O2:Q2)</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="14">
+        <f>R2*2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="20"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="11">
+        <f>SUM(H2:H24)*2+SUM(I2:I24)</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11">
+        <f>SUM(J2:J24)*2+SUM(I10:I13)+H8+I9*2</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
+        <f>SUM(O3:Q3)</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="11"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="14">
+        <f>SUM(K2:K24)</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14">
+        <f>SUM(L2:L24)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="14">
+        <f>SUM(O4:Q4)</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="14"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44FFEB73-5BF8-439E-8DA3-5C3C6DE72758}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -1164,991 +1808,991 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18">
+      <c r="G1" s="16">
         <v>3</v>
       </c>
-      <c r="H1" s="18">
+      <c r="H1" s="16">
         <v>2</v>
       </c>
-      <c r="I1" s="18">
-        <v>1</v>
-      </c>
-      <c r="J1" s="18">
+      <c r="I1" s="16">
+        <v>1</v>
+      </c>
+      <c r="J1" s="16">
         <v>0</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18" t="s">
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="13">
         <v>45934</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16">
-        <v>1</v>
-      </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16">
+      <c r="G2" s="14"/>
+      <c r="H2" s="14">
+        <v>1</v>
+      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14">
         <v>50</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="14">
         <v>17</v>
       </c>
-      <c r="M2" s="16"/>
-      <c r="N2" s="19" t="s">
+      <c r="M2" s="14"/>
+      <c r="N2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O2" s="14">
         <f>SUM(H2:H24)</f>
         <v>10</v>
       </c>
-      <c r="P2" s="16">
+      <c r="P2" s="14">
         <f>SUM(I10:I13)</f>
         <v>4</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="14">
         <f>SUM(J2:J24)+I9</f>
         <v>9</v>
       </c>
-      <c r="R2" s="16">
+      <c r="R2" s="14">
         <f>SUM(O2:Q2)</f>
         <v>23</v>
       </c>
-      <c r="S2" s="16">
+      <c r="S2" s="14">
         <f>R2*2</f>
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
+      <c r="A3" s="20">
         <v>45934</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13">
-        <v>1</v>
-      </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13">
+      <c r="G3" s="11"/>
+      <c r="H3" s="11">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11">
         <v>50</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="11">
         <v>22</v>
       </c>
-      <c r="M3" s="13"/>
-      <c r="N3" s="20" t="s">
+      <c r="M3" s="11"/>
+      <c r="N3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="11">
         <f>SUM(H2:H24)*2+SUM(I2:I24)</f>
         <v>25</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13">
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11">
         <f>SUM(J2:J24)*2+SUM(I10:I13)+H8+I9*2</f>
         <v>23</v>
       </c>
-      <c r="R3" s="13">
+      <c r="R3" s="11">
         <f>SUM(O3:Q3)</f>
         <v>48</v>
       </c>
-      <c r="S3" s="13"/>
+      <c r="S3" s="11"/>
     </row>
     <row r="4" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="13">
         <v>45934</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16">
-        <v>1</v>
-      </c>
-      <c r="K4" s="16">
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14">
+        <v>1</v>
+      </c>
+      <c r="K4" s="14">
         <v>56</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="14">
         <v>63</v>
       </c>
-      <c r="M4" s="16"/>
-      <c r="N4" s="19" t="s">
+      <c r="M4" s="14"/>
+      <c r="N4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="16">
+      <c r="O4" s="14">
         <f>SUM(K2:K24)</f>
         <v>1146</v>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16">
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14">
         <f>SUM(L2:L24)</f>
         <v>1122</v>
       </c>
-      <c r="R4" s="16">
+      <c r="R4" s="14">
         <f>SUM(O4:Q4)</f>
         <v>2268</v>
       </c>
-      <c r="S4" s="16"/>
+      <c r="S4" s="14"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>45955</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13">
-        <v>1</v>
-      </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13">
+      <c r="G5" s="11"/>
+      <c r="H5" s="11">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11">
         <v>50</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="11">
         <v>34</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
     </row>
     <row r="6" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="13">
         <v>46320</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16">
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14">
+        <v>1</v>
+      </c>
+      <c r="K6" s="14">
         <v>50</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="14">
         <v>61</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>45955</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13">
-        <v>1</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11">
+        <v>1</v>
+      </c>
+      <c r="K7" s="11">
         <v>42</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="11">
         <v>50</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
     </row>
     <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="13">
         <v>45976</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16">
-        <v>1</v>
-      </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16">
+      <c r="G8" s="14"/>
+      <c r="H8" s="14">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14">
         <v>73</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="14">
         <v>61</v>
       </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
     </row>
     <row r="9" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="22">
+      <c r="A9" s="20">
         <v>45976</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13">
-        <v>1</v>
-      </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11">
         <v>40</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="11">
         <v>69</v>
       </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="13">
         <v>45997</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16">
-        <v>1</v>
-      </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16">
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14">
+        <v>1</v>
+      </c>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14">
         <v>49</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="14">
         <v>45</v>
       </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>45997</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13">
-        <v>1</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13">
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11">
         <v>45</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="11">
         <v>45</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
     </row>
     <row r="12" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="13">
         <v>45997</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16">
-        <v>1</v>
-      </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16">
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14">
         <v>47</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="14">
         <v>43</v>
       </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>45997</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13">
-        <v>1</v>
-      </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13">
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11">
+        <v>1</v>
+      </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11">
         <v>40</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="11">
         <v>44</v>
       </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
     </row>
     <row r="14" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="13">
         <v>45308</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16">
-        <v>1</v>
-      </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14">
         <v>69</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="14">
         <v>56</v>
       </c>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
     </row>
     <row r="15" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="22">
+      <c r="A15" s="20">
         <v>45674</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13">
-        <v>1</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13">
+      <c r="G15" s="11"/>
+      <c r="H15" s="11">
+        <v>1</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11">
         <v>68</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="11">
         <v>66</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
     </row>
     <row r="16" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="13">
         <v>46060</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16">
+      <c r="G16" s="14"/>
+      <c r="H16" s="14">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14">
         <v>61</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="14">
         <v>62</v>
       </c>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
     </row>
     <row r="17" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="22">
+      <c r="A17" s="20">
         <v>46060</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13">
-        <v>1</v>
-      </c>
-      <c r="K17" s="13">
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11">
+        <v>1</v>
+      </c>
+      <c r="K17" s="11">
         <v>60</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="11">
         <v>63</v>
       </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
     </row>
     <row r="18" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="13">
         <v>46060</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16">
-        <v>1</v>
-      </c>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16">
+      <c r="G18" s="14"/>
+      <c r="H18" s="14">
+        <v>1</v>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14">
         <v>50</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="14">
         <v>36</v>
       </c>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>46109</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13">
-        <v>1</v>
-      </c>
-      <c r="K19" s="13">
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11">
+        <v>1</v>
+      </c>
+      <c r="K19" s="11">
         <v>36</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="11">
         <v>50</v>
       </c>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="13">
         <v>45744</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16">
-        <v>1</v>
-      </c>
-      <c r="K20" s="16">
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14">
+        <v>1</v>
+      </c>
+      <c r="K20" s="14">
         <v>19</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="14">
         <v>50</v>
       </c>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
+      <c r="A21" s="10">
         <v>46109</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13">
-        <v>1</v>
-      </c>
-      <c r="K21" s="13">
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11">
+        <v>1</v>
+      </c>
+      <c r="K21" s="11">
         <v>33</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="11">
         <v>50</v>
       </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="13">
         <v>46137</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16">
-        <v>1</v>
-      </c>
-      <c r="K22" s="16">
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="14">
         <v>47</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="14">
         <v>51</v>
       </c>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
+      <c r="A23" s="10">
         <v>46137</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13">
-        <v>1</v>
-      </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13">
+      <c r="G23" s="11"/>
+      <c r="H23" s="11">
+        <v>1</v>
+      </c>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11">
         <v>50</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="11">
         <v>27</v>
       </c>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
     </row>
     <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="13">
         <v>46137</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16">
-        <v>1</v>
-      </c>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16">
+      <c r="G24" s="14"/>
+      <c r="H24" s="14">
+        <v>1</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14">
         <v>61</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="14">
         <v>57</v>
       </c>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2156,7 +2800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35338555-4C3B-4F48-AD20-7BBDECE7FD0C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -2168,936 +2812,936 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18">
+      <c r="G1" s="16">
         <v>2</v>
       </c>
-      <c r="H1" s="18">
-        <v>1</v>
-      </c>
-      <c r="I1" s="18">
+      <c r="H1" s="16">
+        <v>1</v>
+      </c>
+      <c r="I1" s="16">
         <v>0</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18" t="s">
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="13">
         <v>45577</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16">
-        <v>1</v>
-      </c>
-      <c r="J2" s="16">
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14">
+        <v>1</v>
+      </c>
+      <c r="J2" s="14">
         <v>28</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="14">
         <v>50</v>
       </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="19" t="s">
+      <c r="L2" s="14"/>
+      <c r="M2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N2" s="14">
         <f>SUM(G2:G29)</f>
         <v>8</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O2" s="14">
         <f>SUM(H2:H29)</f>
         <v>0</v>
       </c>
-      <c r="P2" s="16">
+      <c r="P2" s="14">
         <f>SUM(I2:I29)</f>
         <v>15</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="14">
         <f>SUM(N2:P2)</f>
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>45577</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13">
-        <v>1</v>
-      </c>
-      <c r="J3" s="13">
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11">
+        <v>1</v>
+      </c>
+      <c r="J3" s="11">
         <v>44</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="11">
         <v>50</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="20" t="s">
+      <c r="L3" s="11"/>
+      <c r="M3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="11">
         <f>SUM(G2:G29)*2+SUM(H2:H29)</f>
         <v>16</v>
       </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13">
+      <c r="O3" s="11"/>
+      <c r="P3" s="11">
         <f>SUM(I2:I29)*2+SUM(H2:H29)</f>
         <v>30</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="11">
         <f>SUM(N3:P3)</f>
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="13">
         <v>45577</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16">
-        <v>1</v>
-      </c>
-      <c r="J4" s="16">
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14">
+        <v>1</v>
+      </c>
+      <c r="J4" s="14">
         <v>44</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="14">
         <v>51</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="19" t="s">
+      <c r="L4" s="14"/>
+      <c r="M4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="16">
+      <c r="N4" s="14">
         <f>SUM(J2:J24)</f>
         <v>1050</v>
       </c>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16">
+      <c r="O4" s="14"/>
+      <c r="P4" s="14">
         <f>SUM(K2:K24)</f>
         <v>1147</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="14">
         <f>SUM(N4:P4)</f>
         <v>2197</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>45591</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13">
-        <v>1</v>
-      </c>
-      <c r="J5" s="13">
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11">
         <v>31</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="11">
         <v>50</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
     </row>
     <row r="6" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="13">
         <v>45591</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16">
-        <v>1</v>
-      </c>
-      <c r="J6" s="16">
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14">
         <v>51</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="14">
         <v>59</v>
       </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>45591</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="13">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13">
+      <c r="G7" s="11">
+        <v>1</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11">
         <v>50</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="11">
         <v>31</v>
       </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="13">
         <v>45612</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16">
-        <v>1</v>
-      </c>
-      <c r="J8" s="16">
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14">
+        <v>1</v>
+      </c>
+      <c r="J8" s="14">
         <v>29</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="14">
         <v>50</v>
       </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>45612</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="13">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13">
+      <c r="G9" s="11">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11">
         <v>55</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="11">
         <v>51</v>
       </c>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="13">
         <v>45612</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16">
-        <v>1</v>
-      </c>
-      <c r="J10" s="16">
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14">
+        <v>1</v>
+      </c>
+      <c r="J10" s="14">
         <v>30</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="14">
         <v>50</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>45633</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="13">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13">
+      <c r="G11" s="11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11">
         <v>51</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="11">
         <v>39</v>
       </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="13">
         <v>45633</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="16">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16">
+      <c r="G12" s="14">
+        <v>1</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14">
         <v>50</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="14">
         <v>34</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>45633</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="13">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13">
+      <c r="G13" s="11">
+        <v>1</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11">
         <v>58</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="11">
         <v>48</v>
       </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
     </row>
     <row r="14" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="13">
         <v>45676</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="16">
-        <v>1</v>
-      </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16">
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14">
         <v>64</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="14">
         <v>56</v>
       </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>45676</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13">
-        <v>1</v>
-      </c>
-      <c r="J15" s="13">
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11">
+        <v>1</v>
+      </c>
+      <c r="J15" s="11">
         <v>42</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="11">
         <v>50</v>
       </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="13">
         <v>45676</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16">
-        <v>1</v>
-      </c>
-      <c r="J16" s="16">
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14">
+        <v>1</v>
+      </c>
+      <c r="J16" s="14">
         <v>27</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="14">
         <v>50</v>
       </c>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
+      <c r="A17" s="10">
         <v>45696</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13">
-        <v>1</v>
-      </c>
-      <c r="J17" s="13">
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11">
+        <v>1</v>
+      </c>
+      <c r="J17" s="11">
         <v>33</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="11">
         <v>50</v>
       </c>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="13">
         <v>45696</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="G18" s="16">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16">
+      <c r="G18" s="14">
+        <v>1</v>
+      </c>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14">
         <v>50</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="14">
         <v>21</v>
       </c>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>45696</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13">
-        <v>1</v>
-      </c>
-      <c r="J19" s="13">
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11">
+        <v>1</v>
+      </c>
+      <c r="J19" s="11">
         <v>40</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="11">
         <v>50</v>
       </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
     </row>
     <row r="20" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="13">
         <v>45745</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16">
-        <v>1</v>
-      </c>
-      <c r="J20" s="16">
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14">
+        <v>1</v>
+      </c>
+      <c r="J20" s="14">
         <v>55</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="14">
         <v>59</v>
       </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
     </row>
     <row r="21" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
+      <c r="A21" s="10">
         <v>45745</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13">
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11">
         <v>57</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="11">
         <v>52</v>
       </c>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="13">
         <v>45745</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16">
-        <v>1</v>
-      </c>
-      <c r="J22" s="16">
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14">
+        <v>1</v>
+      </c>
+      <c r="J22" s="14">
         <v>31</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="14">
         <v>50</v>
       </c>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
     </row>
     <row r="23" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
+      <c r="A23" s="10">
         <v>45408</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13">
-        <v>1</v>
-      </c>
-      <c r="J23" s="13">
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11">
+        <v>1</v>
+      </c>
+      <c r="J23" s="11">
         <v>68</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="11">
         <v>72</v>
       </c>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
     </row>
     <row r="24" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="13">
         <v>45408</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16">
-        <v>1</v>
-      </c>
-      <c r="J24" s="16">
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14">
+        <v>1</v>
+      </c>
+      <c r="J24" s="14">
         <v>62</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="14">
         <v>74</v>
       </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
@@ -3145,7 +3789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D49F618-7837-4063-847C-00A222FA0E71}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -3157,1048 +3801,1048 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18">
+      <c r="G1" s="16">
         <v>2</v>
       </c>
-      <c r="H1" s="18">
-        <v>1</v>
-      </c>
-      <c r="I1" s="18">
+      <c r="H1" s="16">
+        <v>1</v>
+      </c>
+      <c r="I1" s="16">
         <v>0</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18" t="s">
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>6</v>
       </c>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="13">
         <v>45201</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16">
-        <v>1</v>
-      </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16">
+      <c r="G2" s="14"/>
+      <c r="H2" s="14">
+        <v>1</v>
+      </c>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14">
         <v>46</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="14">
         <v>40</v>
       </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="19" t="s">
+      <c r="L2" s="14"/>
+      <c r="M2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N2" s="14">
         <f>SUM(G2:G27)</f>
         <v>15</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O2" s="14">
         <f>SUM(H2:H27)</f>
         <v>3</v>
       </c>
-      <c r="P2" s="16">
+      <c r="P2" s="14">
         <f>SUM(I2:I27)</f>
         <v>8</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="14">
         <f>SUM(N2:P2)</f>
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>45201</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="13">
-        <v>1</v>
-      </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13">
+      <c r="G3" s="11">
+        <v>1</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11">
         <v>50</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="11">
         <v>29</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="20" t="s">
+      <c r="L3" s="11"/>
+      <c r="M3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="11">
         <f>SUM(G2:G27)*2+SUM(H2:H27)</f>
         <v>33</v>
       </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13">
+      <c r="O3" s="11"/>
+      <c r="P3" s="11">
         <f>SUM(I2:I27)*2+SUM(H2:H27)</f>
         <v>19</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="11">
         <f>SUM(N3:P3)</f>
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="13">
         <v>45201</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16">
-        <v>1</v>
-      </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16">
+      <c r="G4" s="14"/>
+      <c r="H4" s="14">
+        <v>1</v>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14">
         <v>43</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="14">
         <v>48</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="19" t="s">
+      <c r="L4" s="14"/>
+      <c r="M4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="16">
+      <c r="N4" s="14">
         <f>SUM(J2:J27)</f>
         <v>1264</v>
       </c>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16">
+      <c r="O4" s="14"/>
+      <c r="P4" s="14">
         <f>SUM(K2:K27)</f>
         <v>1211</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="14">
         <f>SUM(N4:P4)</f>
         <v>2475</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>45201</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="13">
-        <v>1</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13">
+      <c r="G5" s="11">
+        <v>1</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11">
         <v>51</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="11">
         <v>38</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="13">
         <v>45220</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="16">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16">
+      <c r="G6" s="14">
+        <v>1</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14">
         <v>50</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="14">
         <v>32</v>
       </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>45220</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="13">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13">
+      <c r="G7" s="11">
+        <v>1</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11">
         <v>50</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="11">
         <v>35</v>
       </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="13">
         <v>45220</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="16">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16">
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14">
         <v>50</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="14">
         <v>33</v>
       </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>45220</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13">
-        <v>1</v>
-      </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13">
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
+        <v>1</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11">
         <v>45</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="11">
         <v>43</v>
       </c>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="13">
         <v>45241</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="16">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16">
+      <c r="G10" s="14">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14">
         <v>50</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="14">
         <v>39</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>45241</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="13">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13">
+      <c r="G11" s="11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11">
         <v>51</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="11">
         <v>53</v>
       </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="13">
         <v>45241</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="16">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16">
+      <c r="G12" s="14">
+        <v>1</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14">
         <v>51</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="14">
         <v>46</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>45262</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="13">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13">
+      <c r="G13" s="11">
+        <v>1</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11">
         <v>50</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="11">
         <v>44</v>
       </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
     </row>
     <row r="14" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="13">
         <v>45262</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="16">
-        <v>1</v>
-      </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16">
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14">
         <v>62</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="14">
         <v>56</v>
       </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>45262</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13">
-        <v>1</v>
-      </c>
-      <c r="J15" s="13">
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11">
+        <v>1</v>
+      </c>
+      <c r="J15" s="11">
         <v>48</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="11">
         <v>53</v>
       </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="13">
         <v>45304</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16">
-        <v>1</v>
-      </c>
-      <c r="J16" s="16">
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14">
+        <v>1</v>
+      </c>
+      <c r="J16" s="14">
         <v>37</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="14">
         <v>50</v>
       </c>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
+      <c r="A17" s="10">
         <v>45304</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="13">
-        <v>1</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13">
+      <c r="G17" s="11">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11">
         <v>50</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="11">
         <v>44</v>
       </c>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
     </row>
     <row r="18" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="13">
         <v>45304</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="16">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16">
+      <c r="G18" s="14">
+        <v>1</v>
+      </c>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14">
         <v>56</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="14">
         <v>63</v>
       </c>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>45325</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="13">
-        <v>1</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13">
+      <c r="G19" s="11">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11">
         <v>50</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="11">
         <v>39</v>
       </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
     </row>
     <row r="20" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="13">
         <v>45325</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16">
-        <v>1</v>
-      </c>
-      <c r="J20" s="16">
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14">
+        <v>1</v>
+      </c>
+      <c r="J20" s="14">
         <v>60</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="14">
         <v>60</v>
       </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
     </row>
     <row r="21" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
+      <c r="A21" s="10">
         <v>45325</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13">
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11">
         <v>60</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="11">
         <v>54</v>
       </c>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="13">
         <v>45374</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16">
-        <v>1</v>
-      </c>
-      <c r="J22" s="16">
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14">
+        <v>1</v>
+      </c>
+      <c r="J22" s="14">
         <v>34</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="14">
         <v>50</v>
       </c>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
+      <c r="A23" s="10">
         <v>45374</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13">
-        <v>1</v>
-      </c>
-      <c r="J23" s="13">
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11">
+        <v>1</v>
+      </c>
+      <c r="J23" s="11">
         <v>35</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="11">
         <v>50</v>
       </c>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="13">
         <v>45374</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16">
-        <v>1</v>
-      </c>
-      <c r="J24" s="16">
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14">
+        <v>1</v>
+      </c>
+      <c r="J24" s="14">
         <v>38</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="14">
         <v>50</v>
       </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="12">
+      <c r="A25" s="10">
         <v>45395</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="13" t="s">
+      <c r="B25" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G25" s="13">
-        <v>1</v>
-      </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13">
+      <c r="G25" s="11">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11">
         <v>50</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="11">
         <v>42</v>
       </c>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
     </row>
     <row r="26" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="13">
         <v>45395</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16">
-        <v>1</v>
-      </c>
-      <c r="J26" s="16">
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14">
+        <v>1</v>
+      </c>
+      <c r="J26" s="14">
         <v>58</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="14">
         <v>70</v>
       </c>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="12">
+      <c r="A27" s="10">
         <v>45395</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="13" t="s">
+      <c r="B27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13">
-        <v>1</v>
-      </c>
-      <c r="J27" s="13">
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11">
+        <v>1</v>
+      </c>
+      <c r="J27" s="11">
         <v>39</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="11">
         <v>50</v>
       </c>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/B-pojat.xlsx
+++ b/B-pojat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC0BBA9-C86F-4891-8ABB-E174A534FEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B6E0E6-BCFD-4535-9DF5-232A27A66125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1596" yWindow="540" windowWidth="21072" windowHeight="12948" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="3048" yWindow="1392" windowWidth="19104" windowHeight="11892" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="B 2023-2027" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="148">
   <si>
     <t>päivä</t>
   </si>
@@ -478,6 +478,12 @@
   </si>
   <si>
     <t>2026-2027</t>
+  </si>
+  <si>
+    <t>Pirkat Blue</t>
+  </si>
+  <si>
+    <t>PuMa 2</t>
   </si>
 </sst>
 </file>
@@ -1118,35 +1124,35 @@
         <v>145</v>
       </c>
       <c r="C5" s="23">
-        <f>'B 2026-2027'!R3</f>
+        <f>'B 2026-2027'!R2</f>
         <v>0</v>
       </c>
       <c r="D5" s="23">
-        <f>'B 2026-2027'!O3</f>
+        <f>'B 2026-2027'!O2</f>
         <v>0</v>
       </c>
       <c r="E5" s="23">
-        <f>'B 2026-2027'!P3</f>
+        <f>'B 2026-2027'!P2</f>
         <v>0</v>
       </c>
       <c r="F5" s="23">
-        <f>'B 2026-2027'!Q3</f>
+        <f>'B 2026-2027'!Q2</f>
         <v>0</v>
       </c>
       <c r="G5" s="23">
-        <f>'B 2026-2027'!O4</f>
+        <f>'B 2026-2027'!O2</f>
         <v>0</v>
       </c>
       <c r="H5" s="23">
-        <f>'B 2025-2026'!Q4</f>
-        <v>1122</v>
+        <f>'B 2026-2027'!Q2</f>
+        <v>0</v>
       </c>
       <c r="I5" s="23">
-        <f>'B 2025-2026'!O5</f>
+        <f>'B 2026-2027'!O2</f>
         <v>0</v>
       </c>
       <c r="J5" s="23">
-        <f>'B 2025-2026'!Q5</f>
+        <f>'B 2026-2027'!Q2</f>
         <v>0</v>
       </c>
       <c r="K5" s="22"/>
@@ -1178,7 +1184,7 @@
       </c>
       <c r="H6" s="24">
         <f t="shared" si="0"/>
-        <v>1194</v>
+        <v>72</v>
       </c>
       <c r="I6" s="24">
         <f t="shared" si="0"/>
@@ -1262,7 +1268,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
-        <v>45934</v>
+        <v>46312</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>7</v>
@@ -1270,7 +1276,9 @@
       <c r="C2" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>146</v>
+      </c>
       <c r="E2" s="15"/>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
@@ -1305,10 +1313,18 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="A3" s="20">
+        <v>46312</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>147</v>
+      </c>
       <c r="E3" s="12"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
@@ -1337,10 +1353,18 @@
       <c r="S3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="A4" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="E4" s="15"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
